--- a/docs/downloads/20261008_Seputeh Hills_Teduh Weekly Update.xlsx
+++ b/docs/downloads/20261008_Seputeh Hills_Teduh Weekly Update.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AT11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,10 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="9" customWidth="1" min="41" max="41"/>
     <col width="9" customWidth="1" min="42" max="42"/>
-    <col width="42" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="43" max="43"/>
+    <col width="9" customWidth="1" min="44" max="44"/>
+    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="42" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -585,8 +588,11 @@
       <c r="AK3" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="AN3" s="4" t="n">
+      <c r="AN3" s="3" t="n">
         <v>46297</v>
+      </c>
+      <c r="AQ3" s="4" t="n">
+        <v>46304</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -788,22 +794,37 @@
           <t>%</t>
         </is>
       </c>
-      <c r="AN4" s="6" t="inlineStr">
+      <c r="AN4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="AO4" s="6" t="inlineStr">
+      <c r="AO4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="AP4" s="6" t="inlineStr">
+      <c r="AP4" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="AQ4" s="5" t="inlineStr">
+      <c r="AQ4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="AR4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="AS4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AT4" s="5" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
@@ -954,18 +975,29 @@
         <f>AL5/$D$5</f>
         <v/>
       </c>
-      <c r="AN5" s="12">
+      <c r="AN5" s="10">
         <f>AO5-AL5</f>
         <v/>
       </c>
-      <c r="AO5" s="12" t="n">
+      <c r="AO5" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="AP5" s="13">
+      <c r="AP5" s="11">
         <f>AO5/$D$5</f>
         <v/>
       </c>
-      <c r="AQ5" s="8" t="inlineStr">
+      <c r="AQ5" s="12">
+        <f>AR5-AO5</f>
+        <v/>
+      </c>
+      <c r="AR5" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS5" s="13">
+        <f>AR5/$D$5</f>
+        <v/>
+      </c>
+      <c r="AT5" s="8" t="inlineStr">
         <is>
           <t>Big unit (5,533 to Penthouse 19,031sqft)</t>
         </is>
@@ -1116,18 +1148,29 @@
         <f>AL6/$D$6</f>
         <v/>
       </c>
-      <c r="AN6" s="12">
+      <c r="AN6" s="10">
         <f>AO6-AL6</f>
         <v/>
       </c>
-      <c r="AO6" s="12" t="n">
+      <c r="AO6" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="AP6" s="13">
+      <c r="AP6" s="11">
         <f>AO6/$D$6</f>
         <v/>
       </c>
-      <c r="AQ6" s="8" t="inlineStr">
+      <c r="AQ6" s="12">
+        <f>AR6-AO6</f>
+        <v/>
+      </c>
+      <c r="AR6" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="AS6" s="13">
+        <f>AR6/$D$6</f>
+        <v/>
+      </c>
+      <c r="AT6" s="8" t="inlineStr">
         <is>
           <t>Big unit (3,380 to 4,090sqft  &amp; Penthouse 7,459sqft).</t>
         </is>
@@ -1278,18 +1321,29 @@
         <f>AL7/$D$7</f>
         <v/>
       </c>
-      <c r="AN7" s="12">
+      <c r="AN7" s="10">
         <f>AO7-AL7</f>
         <v/>
       </c>
-      <c r="AO7" s="12" t="n">
+      <c r="AO7" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="AP7" s="13">
+      <c r="AP7" s="11">
         <f>AO7/$D$7</f>
         <v/>
       </c>
-      <c r="AQ7" s="8" t="inlineStr">
+      <c r="AQ7" s="12">
+        <f>AR7-AO7</f>
+        <v/>
+      </c>
+      <c r="AR7" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS7" s="13">
+        <f>AR7/$D$7</f>
+        <v/>
+      </c>
+      <c r="AT7" s="8" t="inlineStr">
         <is>
           <t>Small unit (452 to 1,679 sq ft)</t>
         </is>
@@ -1440,18 +1494,29 @@
         <f>AL8/$D$8</f>
         <v/>
       </c>
-      <c r="AN8" s="12">
+      <c r="AN8" s="10">
         <f>AO8-AL8</f>
         <v/>
       </c>
-      <c r="AO8" s="12" t="n">
+      <c r="AO8" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="AP8" s="13">
+      <c r="AP8" s="11">
         <f>AO8/$D$8</f>
         <v/>
       </c>
-      <c r="AQ8" s="8" t="inlineStr">
+      <c r="AQ8" s="12">
+        <f>AR8-AO8</f>
+        <v/>
+      </c>
+      <c r="AR8" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS8" s="13">
+        <f>AR8/$D$8</f>
+        <v/>
+      </c>
+      <c r="AT8" s="8" t="inlineStr">
         <is>
           <t>4-storey Villa (4,854 to 5,157 sq ft); left 3 bumi units</t>
         </is>
@@ -1602,18 +1667,29 @@
         <f>AL9/$D$9</f>
         <v/>
       </c>
-      <c r="AN9" s="12">
+      <c r="AN9" s="10">
         <f>AO9-AL9</f>
         <v/>
       </c>
-      <c r="AO9" s="12" t="n">
+      <c r="AO9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="AP9" s="13">
+      <c r="AP9" s="11">
         <f>AO9/$D$9</f>
         <v/>
       </c>
-      <c r="AQ9" s="8" t="inlineStr">
+      <c r="AQ9" s="12">
+        <f>AR9-AO9</f>
+        <v/>
+      </c>
+      <c r="AR9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS9" s="13">
+        <f>AR9/$D$9</f>
+        <v/>
+      </c>
+      <c r="AT9" s="8" t="inlineStr">
         <is>
           <t>Big unit (1,648 to 3,856 sq ft)</t>
         </is>
@@ -1754,18 +1830,29 @@
         <f>AL10/$D$10</f>
         <v/>
       </c>
-      <c r="AN10" s="12">
+      <c r="AN10" s="10">
         <f>AO10-AL10</f>
         <v/>
       </c>
-      <c r="AO10" s="12" t="n">
+      <c r="AO10" s="10" t="n">
         <v>359</v>
       </c>
-      <c r="AP10" s="13">
+      <c r="AP10" s="11">
         <f>AO10/$D$10</f>
         <v/>
       </c>
-      <c r="AQ10" s="8" t="inlineStr">
+      <c r="AQ10" s="12">
+        <f>AR10-AO10</f>
+        <v/>
+      </c>
+      <c r="AR10" s="12" t="n">
+        <v>359</v>
+      </c>
+      <c r="AS10" s="13">
+        <f>AR10/$D$10</f>
+        <v/>
+      </c>
+      <c r="AT10" s="8" t="inlineStr">
         <is>
           <t>Big unit (2,842 to 10,613 sq ft)</t>
         </is>
@@ -1874,21 +1961,32 @@
         <f>AL11/$D$11</f>
         <v/>
       </c>
-      <c r="AN11" s="12">
+      <c r="AN11" s="10">
         <f>AO11-AL11</f>
         <v/>
       </c>
-      <c r="AO11" s="12" t="n">
+      <c r="AO11" s="10" t="n">
         <v>112</v>
       </c>
-      <c r="AP11" s="13">
+      <c r="AP11" s="11">
         <f>AO11/$D$11</f>
         <v/>
       </c>
-      <c r="AQ11" s="8" t="inlineStr"/>
+      <c r="AQ11" s="12">
+        <f>AR11-AO11</f>
+        <v/>
+      </c>
+      <c r="AR11" s="12" t="n">
+        <v>139</v>
+      </c>
+      <c r="AS11" s="13">
+        <f>AR11/$D$11</f>
+        <v/>
+      </c>
+      <c r="AT11" s="8" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="Y3:AA3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="AB3:AD3"/>
@@ -1901,6 +1999,7 @@
     <mergeCell ref="AN3:AP3"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="P3:R3"/>
+    <mergeCell ref="AQ3:AS3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
